--- a/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.92</v>
@@ -1786,7 +1786,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.23</v>
@@ -2222,7 +2222,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>1.72</v>
@@ -3312,7 +3312,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>1.39</v>
@@ -3527,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.92</v>
@@ -4184,7 +4184,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>1.22</v>
@@ -4402,7 +4402,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR18" t="n">
         <v>2.13</v>
@@ -4617,7 +4617,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.08</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.17</v>
@@ -5274,7 +5274,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.89</v>
@@ -6797,10 +6797,10 @@
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR29" t="n">
         <v>1.63</v>
@@ -7233,10 +7233,10 @@
         <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
         <v>2.97</v>
@@ -8759,7 +8759,7 @@
         <v>0.25</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.08</v>
@@ -8980,7 +8980,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR39" t="n">
         <v>1.94</v>
@@ -9413,7 +9413,7 @@
         <v>0.75</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.92</v>
@@ -10724,7 +10724,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR47" t="n">
         <v>1.37</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.55</v>
@@ -12465,7 +12465,7 @@
         <v>0.83</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.55</v>
@@ -12901,7 +12901,7 @@
         <v>1.2</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.91</v>
@@ -13776,7 +13776,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR61" t="n">
         <v>1.35</v>
@@ -15299,7 +15299,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.17</v>
@@ -15517,7 +15517,7 @@
         <v>2.17</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.75</v>
@@ -15738,7 +15738,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR70" t="n">
         <v>1.77</v>
@@ -17264,7 +17264,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR77" t="n">
         <v>1.64</v>
@@ -17479,7 +17479,7 @@
         <v>1.86</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.75</v>
@@ -17697,7 +17697,7 @@
         <v>0.29</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.23</v>
@@ -17918,7 +17918,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR80" t="n">
         <v>1.59</v>
@@ -18572,7 +18572,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR83" t="n">
         <v>1.66</v>
@@ -19659,10 +19659,10 @@
         <v>0.88</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR88" t="n">
         <v>2.01</v>
@@ -20095,10 +20095,10 @@
         <v>1.13</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR90" t="n">
         <v>1.86</v>
@@ -20749,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.92</v>
@@ -21624,7 +21624,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR97" t="n">
         <v>1.44</v>
@@ -22493,7 +22493,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.23</v>
@@ -22714,7 +22714,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.4</v>
@@ -23583,7 +23583,7 @@
         <v>1.9</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.92</v>
@@ -23804,7 +23804,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR107" t="n">
         <v>1.75</v>
@@ -24019,7 +24019,7 @@
         <v>1.27</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.08</v>
@@ -24237,7 +24237,7 @@
         <v>1.27</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.17</v>
@@ -25112,7 +25112,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR113" t="n">
         <v>1.43</v>
@@ -26495,6 +26495,442 @@
         <v>3.86</v>
       </c>
       <c r="BP119" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>7963522</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F120" t="n">
+        <v>24</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>['13', '90+6']</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U120" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X120" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>7963476</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>46082.55208333334</v>
+      </c>
+      <c r="F121" t="n">
+        <v>24</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" t="n">
+        <v>4</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2</v>
+      </c>
+      <c r="N121" t="n">
+        <v>6</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>['7', '17', '62', '73']</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>['36', '89']</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S121" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X121" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP121" t="n">
         <v>1.17</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
@@ -26659,13 +26659,13 @@
         <v>5</v>
       </c>
       <c r="AX120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY120" t="n">
         <v>7</v>
       </c>
       <c r="AZ120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA120" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.23</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.67</v>
@@ -2658,7 +2658,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR15" t="n">
         <v>2.01</v>
@@ -5056,7 +5056,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR21" t="n">
         <v>1.96</v>
@@ -5271,7 +5271,7 @@
         <v>1.25</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -5925,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR25" t="n">
         <v>1.21</v>
@@ -7669,10 +7669,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR33" t="n">
         <v>1.44</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.92</v>
@@ -8105,10 +8105,10 @@
         <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR35" t="n">
         <v>1.76</v>
@@ -9195,10 +9195,10 @@
         <v>0.67</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR40" t="n">
         <v>1.41</v>
@@ -9631,10 +9631,10 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR42" t="n">
         <v>1.71</v>
@@ -10070,7 +10070,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR44" t="n">
         <v>1.92</v>
@@ -10285,7 +10285,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.91</v>
@@ -10503,7 +10503,7 @@
         <v>2.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.92</v>
@@ -11160,7 +11160,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR49" t="n">
         <v>2.45</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.75</v>
@@ -11593,10 +11593,10 @@
         <v>0.75</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR51" t="n">
         <v>1.41</v>
@@ -11811,7 +11811,7 @@
         <v>2.25</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.75</v>
@@ -12029,7 +12029,7 @@
         <v>0.4</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.08</v>
@@ -12468,7 +12468,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.23</v>
@@ -13558,7 +13558,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR60" t="n">
         <v>1.86</v>
@@ -13773,7 +13773,7 @@
         <v>1.2</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.67</v>
@@ -13991,7 +13991,7 @@
         <v>0.2</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.23</v>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.92</v>
@@ -14430,7 +14430,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR64" t="n">
         <v>1.78</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.92</v>
@@ -15302,7 +15302,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR68" t="n">
         <v>2.07</v>
@@ -15953,7 +15953,7 @@
         <v>0.83</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.08</v>
@@ -16174,7 +16174,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR72" t="n">
         <v>1.36</v>
@@ -16392,7 +16392,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR73" t="n">
         <v>1.92</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.92</v>
@@ -16825,7 +16825,7 @@
         <v>0.86</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.91</v>
@@ -17043,7 +17043,7 @@
         <v>1.43</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.92</v>
@@ -18354,7 +18354,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR82" t="n">
         <v>1.38</v>
@@ -18787,7 +18787,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.75</v>
@@ -20313,7 +20313,7 @@
         <v>0.88</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.91</v>
@@ -20531,7 +20531,7 @@
         <v>0.22</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.23</v>
@@ -21403,10 +21403,10 @@
         <v>0.89</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR96" t="n">
         <v>1.36</v>
@@ -21621,7 +21621,7 @@
         <v>0.78</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.67</v>
@@ -21839,7 +21839,7 @@
         <v>1.89</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.75</v>
@@ -22060,7 +22060,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR99" t="n">
         <v>1.65</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ102" t="n">
         <v>1</v>
@@ -23368,7 +23368,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR105" t="n">
         <v>1.66</v>
@@ -24240,7 +24240,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR109" t="n">
         <v>1.74</v>
@@ -24455,7 +24455,7 @@
         <v>0.18</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.23</v>
@@ -25109,7 +25109,7 @@
         <v>0.9</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ113" t="n">
         <v>1</v>
@@ -25327,10 +25327,10 @@
         <v>0.6</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR114" t="n">
         <v>1.4</v>
@@ -26932,6 +26932,660 @@
       </c>
       <c r="BP121" t="n">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>7963524</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>46087.58333333334</v>
+      </c>
+      <c r="F122" t="n">
+        <v>25</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V122" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X122" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>7963500</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F123" t="n">
+        <v>25</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>4</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>['13', '76']</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>['55', '74']</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U123" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V123" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X123" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>7963376</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Croatia Prva HNL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>46088.55208333334</v>
+      </c>
+      <c r="F124" t="n">
+        <v>25</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S124" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V124" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W124" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X124" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Croatia Prva HNL_20252026.xlsx
@@ -27322,13 +27322,13 @@
         <v>12</v>
       </c>
       <c r="BA123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB123" t="n">
         <v>5</v>
       </c>
       <c r="BC123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD123" t="n">
         <v>1.99</v>
